--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,57 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96790345</v>
+        <v>136858660</v>
       </c>
       <c r="B2" t="n">
-        <v>93213</v>
+        <v>79142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Getingfors by, 700 m S om, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550303</v>
+        <v>550202</v>
       </c>
       <c r="R2" t="n">
-        <v>6964628</v>
+        <v>6964687</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,75 +771,75 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>äldre renbetad tallskog på sandig morän</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96790345</t>
+          <t>https://artportalen.se/Sighting/136858660</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113232820</v>
+        <v>96790345</v>
       </c>
       <c r="B3" t="n">
-        <v>93191</v>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
+          <t>Getingfors by, 700 m S om, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550251</v>
+        <v>550303</v>
       </c>
       <c r="R3" t="n">
-        <v>6964726</v>
+        <v>6964628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +866,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,26 +882,2305 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>äldre renbetad tallskog på sandig morän</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790345</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136858642</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93427</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>550348</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6964651</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858642</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136858646</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93427</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>550306</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6964627</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858646</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113232820</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>550251</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6964726</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Pontus Wallén</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113232820</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136858643</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>550338</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6964650</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858643</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136858644</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>550322</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6964635</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858644</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136858645</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>550310</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6964632</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858645</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136858647</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>550290</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6964629</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858647</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136858648</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>550285</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6964614</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858648</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136858649</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>550276</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6964609</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858649</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136858655</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>550189</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6964532</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858655</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136858657</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>550156</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6964603</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858657</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136858658</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>550171</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6964601</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858658</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136858659</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>550190</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6964638</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858659</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136858662</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>550261</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6964705</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858662</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136858650</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>550261</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6964597</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858650</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136858654</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>550198</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6964553</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858654</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136858652</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>550209</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6964571</v>
+      </c>
+      <c r="S20" t="n">
+        <v>7</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858652</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136858661</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>550205</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6964688</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858661</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136858653</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>550198</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6964553</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858653</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136858651</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>550261</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6964597</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858651</t>
         </is>
       </c>
     </row>
@@ -908,6 +3188,26 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858660</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136858650</v>
       </c>
       <c r="B18" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136858654</v>
       </c>
       <c r="B19" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>136858652</v>
       </c>
       <c r="B20" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136858661</v>
       </c>
       <c r="B21" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136858653</v>
       </c>
       <c r="B22" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136858651</v>
       </c>
       <c r="B23" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858660</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136858650</v>
       </c>
       <c r="B18" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136858654</v>
       </c>
       <c r="B19" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>136858652</v>
       </c>
       <c r="B20" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136858661</v>
       </c>
       <c r="B21" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136858653</v>
       </c>
       <c r="B22" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136858651</v>
       </c>
       <c r="B23" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858660</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136858650</v>
       </c>
       <c r="B18" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136858654</v>
       </c>
       <c r="B19" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>136858652</v>
       </c>
       <c r="B20" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136858661</v>
       </c>
       <c r="B21" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136858653</v>
       </c>
       <c r="B22" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136858651</v>
       </c>
       <c r="B23" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858660</v>
       </c>
       <c r="B2" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136858650</v>
       </c>
       <c r="B18" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136858654</v>
       </c>
       <c r="B19" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>136858652</v>
       </c>
       <c r="B20" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136858661</v>
       </c>
       <c r="B21" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136858653</v>
       </c>
       <c r="B22" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136858651</v>
       </c>
       <c r="B23" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858660</v>
       </c>
       <c r="B2" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136858650</v>
       </c>
       <c r="B18" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136858654</v>
       </c>
       <c r="B19" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>136858652</v>
       </c>
       <c r="B20" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136858661</v>
       </c>
       <c r="B21" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136858653</v>
       </c>
       <c r="B22" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136858651</v>
       </c>
       <c r="B23" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858660</v>
       </c>
       <c r="B2" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136858650</v>
       </c>
       <c r="B18" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136858654</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>136858652</v>
       </c>
       <c r="B20" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136858661</v>
       </c>
       <c r="B21" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136858653</v>
       </c>
       <c r="B22" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136858651</v>
       </c>
       <c r="B23" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858660</v>
       </c>
       <c r="B2" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136858650</v>
       </c>
       <c r="B18" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136858654</v>
       </c>
       <c r="B19" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>136858652</v>
       </c>
       <c r="B20" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136858661</v>
       </c>
       <c r="B21" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136858653</v>
       </c>
       <c r="B22" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136858651</v>
       </c>
       <c r="B23" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858660</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136858650</v>
       </c>
       <c r="B18" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136858654</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>136858652</v>
       </c>
       <c r="B20" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136858661</v>
       </c>
       <c r="B21" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136858653</v>
       </c>
       <c r="B22" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136858651</v>
       </c>
       <c r="B23" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858660</v>
       </c>
       <c r="B2" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136858650</v>
       </c>
       <c r="B18" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136858654</v>
       </c>
       <c r="B19" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>136858652</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136858661</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136858653</v>
       </c>
       <c r="B22" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136858651</v>
       </c>
       <c r="B23" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858660</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136858650</v>
       </c>
       <c r="B18" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136858654</v>
       </c>
       <c r="B19" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>136858652</v>
       </c>
       <c r="B20" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136858661</v>
       </c>
       <c r="B21" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136858653</v>
       </c>
       <c r="B22" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136858651</v>
       </c>
       <c r="B23" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 54051-2023 artfynd.xlsx
+++ b/artfynd/A 54051-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858660</v>
       </c>
       <c r="B2" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858642</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136858646</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136858643</v>
       </c>
       <c r="B7" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136858644</v>
       </c>
       <c r="B8" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136858645</v>
       </c>
       <c r="B9" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136858647</v>
       </c>
       <c r="B10" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>136858648</v>
       </c>
       <c r="B11" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136858649</v>
       </c>
       <c r="B12" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>136858655</v>
       </c>
       <c r="B13" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>136858657</v>
       </c>
       <c r="B14" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136858658</v>
       </c>
       <c r="B15" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>136858659</v>
       </c>
       <c r="B16" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136858662</v>
       </c>
       <c r="B17" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136858650</v>
       </c>
       <c r="B18" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136858654</v>
       </c>
       <c r="B19" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>136858652</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136858661</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136858653</v>
       </c>
       <c r="B22" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136858651</v>
       </c>
       <c r="B23" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
